--- a/data/trans_dic/P36BPD07_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD07_R-Edad-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>63,56%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>61,57; 71,44</t>
+          <t>61,83; 71,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,35; 74,64</t>
+          <t>57,6; 71,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69,72; 78,41</t>
+          <t>69,28; 77,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56,56; 71,21</t>
+          <t>55,37; 69,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66,8; 73,22</t>
+          <t>66,77; 73,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,1; 71,23</t>
+          <t>58,76; 68,85</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>69,35%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>72,57; 79,38</t>
+          <t>71,9; 79,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56,24; 68,72</t>
+          <t>58,54; 69,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73,77; 80,74</t>
+          <t>73,84; 80,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73,28; 87,18</t>
+          <t>70,16; 78,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>74,26; 79,0</t>
+          <t>74,21; 79,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,04; 78,57</t>
+          <t>65,79; 72,75</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>70,91%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79,73; 85,98</t>
+          <t>80,02; 85,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66,85; 74,71</t>
+          <t>65,53; 73,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,39; 84,37</t>
+          <t>78,46; 84,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69,29; 75,64</t>
+          <t>69,12; 75,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80,18; 84,24</t>
+          <t>80,07; 84,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,86; 73,97</t>
+          <t>68,4; 73,31</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>73,4%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,37; 88,03</t>
+          <t>82,58; 88,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>70,11; 91,64</t>
+          <t>66,93; 74,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86,53; 91,52</t>
+          <t>86,49; 91,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75,24; 81,87</t>
+          <t>73,19; 78,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>85,47; 89,33</t>
+          <t>85,22; 89,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,0; 86,4</t>
+          <t>71,28; 75,71</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,37%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>93,44; 97,59</t>
+          <t>93,33; 97,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,34; 78,11</t>
+          <t>71,4; 77,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91,75; 96,41</t>
+          <t>91,71; 96,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77,35; 82,58</t>
+          <t>77,36; 82,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>93,5; 96,55</t>
+          <t>93,31; 96,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,32; 79,6</t>
+          <t>75,1; 79,24</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>81,52%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>94,58; 98,48</t>
+          <t>94,5; 98,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>76,33; 83,15</t>
+          <t>76,32; 83,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95,86; 98,91</t>
+          <t>95,81; 98,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>82,38; 95,6</t>
+          <t>80,23; 85,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>95,85; 98,34</t>
+          <t>95,76; 98,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81,1; 92,67</t>
+          <t>79,27; 83,39</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,34%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>93,96; 98,42</t>
+          <t>94,24; 98,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>75,53; 82,67</t>
+          <t>74,86; 82,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94,58; 98,47</t>
+          <t>94,52; 98,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82,07; 87,2</t>
+          <t>82,18; 86,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,27; 98,14</t>
+          <t>95,25; 98,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,55; 84,68</t>
+          <t>80,41; 84,27</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>73,95%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>83,09; 85,7</t>
+          <t>83,16; 85,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>71,27; 79,78</t>
+          <t>69,74; 73,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85,58; 87,81</t>
+          <t>85,58; 87,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76,94; 82,6</t>
+          <t>74,95; 77,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>84,78; 86,46</t>
+          <t>84,7; 86,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>74,64; 79,51</t>
+          <t>72,88; 75,07</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>267552</t>
+          <t>263464</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>202181</t>
+          <t>226144</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>469732</t>
+          <t>489608</t>
         </is>
       </c>
     </row>
@@ -1425,32 +1425,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>256927; 298145</t>
+          <t>258008; 296497</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>233376; 298542</t>
+          <t>234903; 291776</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>275901; 310326</t>
+          <t>274163; 307326</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>177161; 223035</t>
+          <t>200707; 250130</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>543164; 595345</t>
+          <t>542858; 594923</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>428618; 507983</t>
+          <t>452596; 530337</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>266454</t>
+          <t>306363</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399050</t>
+          <t>371245</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>665504</t>
+          <t>677608</t>
         </is>
       </c>
     </row>
@@ -1543,32 +1543,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>427755; 467920</t>
+          <t>423817; 465783</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>238200; 291061</t>
+          <t>279149; 332208</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>414991; 454211</t>
+          <t>415416; 454014</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>374092; 445042</t>
+          <t>350878; 391357</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>855458; 910042</t>
+          <t>854875; 910471</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>626218; 733902</t>
+          <t>642775; 710784</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>378423</t>
+          <t>430766</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>392111</t>
+          <t>448142</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>770534</t>
+          <t>878907</t>
         </is>
       </c>
     </row>
@@ -1661,32 +1661,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>531846; 573504</t>
+          <t>533747; 570118</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>357789; 399866</t>
+          <t>406056; 456147</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>516331; 555728</t>
+          <t>516807; 555406</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>375138; 409535</t>
+          <t>428453; 466768</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1062915; 1116768</t>
+          <t>1061406; 1116303</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>741351; 796421</t>
+          <t>847784; 908632</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>703653</t>
+          <t>497066</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>554450</t>
+          <t>557281</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1258103</t>
+          <t>1054348</t>
         </is>
       </c>
     </row>
@@ -1779,32 +1779,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>531408; 567929</t>
+          <t>532756; 568779</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>622445; 813587</t>
+          <t>468892; 520109</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>557963; 590136</t>
+          <t>557667; 589273</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>535555; 582761</t>
+          <t>538510; 575050</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1102525; 1152352</t>
+          <t>1099280; 1150401</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1183774; 1382047</t>
+          <t>1023828; 1087557</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>418603</t>
+          <t>453479</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>437378</t>
+          <t>485982</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>855982</t>
+          <t>939462</t>
         </is>
       </c>
     </row>
@@ -1897,32 +1897,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>439034; 458538</t>
+          <t>438512; 458259</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>398366; 436189</t>
+          <t>433044; 472891</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>453668; 476675</t>
+          <t>453438; 475939</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>423021; 451604</t>
+          <t>470152; 500685</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>901583; 930986</t>
+          <t>899798; 931134</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>832504; 879791</t>
+          <t>911855; 962183</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>293141</t>
+          <t>324633</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>539889</t>
+          <t>363354</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>833031</t>
+          <t>687987</t>
         </is>
       </c>
     </row>
@@ -2015,32 +2015,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>314196; 327157</t>
+          <t>313953; 326587</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>280330; 305351</t>
+          <t>309852; 337150</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>361063; 372540</t>
+          <t>360880; 372536</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>500242; 580485</t>
+          <t>351351; 374958</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>679480; 697112</t>
+          <t>678810; 696716</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>790249; 902993</t>
+          <t>668994; 703763</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>224349</t>
+          <t>245232</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>361242</t>
+          <t>392272</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>585592</t>
+          <t>637504</t>
         </is>
       </c>
     </row>
@@ -2133,32 +2133,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>235036; 246185</t>
+          <t>235726; 246586</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>213580; 233759</t>
+          <t>232215; 256919</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>368286; 383467</t>
+          <t>368058; 383214</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>349018; 370856</t>
+          <t>381316; 402771</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>609325; 627651</t>
+          <t>609190; 627995</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>570301; 599581</t>
+          <t>622505; 652401</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2552177</t>
+          <t>2521004</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2886300</t>
+          <t>2844420</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5438477</t>
+          <t>5365424</t>
         </is>
       </c>
     </row>
@@ -2251,32 +2251,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2800989; 2889160</t>
+          <t>2803345; 2886551</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2462346; 2756369</t>
+          <t>2460119; 2583832</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3014471; 3093012</t>
+          <t>3014342; 3093238</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2813060; 3020270</t>
+          <t>2794219; 2894783</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5843895; 5960210</t>
+          <t>5838447; 5961622</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5307759; 5654380</t>
+          <t>5287905; 5446729</t>
         </is>
       </c>
     </row>
